--- a/input-rsp/RSP_Inbound_May26.xlsx
+++ b/input-rsp/RSP_Inbound_May26.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DQ38"/>
+  <dimension ref="A1:DQ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1116,7 +1116,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>203May</t>
+          <t>901IBMay</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1126,11 +1126,11 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>20000</v>
+        <v>200000</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -1139,116 +1139,124 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>Nok</t>
+          <t>Piti</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>Helper</t>
+          <t>Cross</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>2030000000203</t>
+          <t>2020000000901</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>Domestic Helper</t>
+          <t>Self-Employed</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20600000</t>
+          <t>902IBMay</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>09:30:00</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>5000</v>
+        <v>100000</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>ATH160206</t>
+          <t>ATH160001</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>Border</t>
+          <t>Somchai</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>Risk</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>2060000000206</t>
-        </is>
-      </c>
-      <c r="CK5" t="inlineStr"/>
+          <t>2020000000902</t>
+        </is>
+      </c>
+      <c r="CK5" t="inlineStr">
+        <is>
+          <t>Self-Employed</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20600001</t>
+          <t>203May</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5000</v>
+        <v>20000</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>ATH160206</t>
+          <t>ATH160001</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>Border</t>
+          <t>Nok</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>Risk</t>
+          <t>Helper</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>2060000000206</t>
-        </is>
-      </c>
-      <c r="CK6" t="inlineStr"/>
+          <t>2030000000203</t>
+        </is>
+      </c>
+      <c r="CK6" t="inlineStr">
+        <is>
+          <t>Domestic Helper</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20600002</t>
+          <t>20600000</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1284,12 +1292,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20600003</t>
+          <t>20600001</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1325,12 +1333,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20600004</t>
+          <t>20600002</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1366,12 +1374,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20600005</t>
+          <t>20600003</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1407,12 +1415,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20600006</t>
+          <t>20600004</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1448,12 +1456,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20600007</t>
+          <t>20600005</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1489,12 +1497,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20600008</t>
+          <t>20600006</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1530,12 +1538,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20600009</t>
+          <t>20600007</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1571,12 +1579,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20600010</t>
+          <t>20600008</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1612,12 +1620,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20600011</t>
+          <t>20600009</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1653,12 +1661,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20600012</t>
+          <t>20600010</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1694,12 +1702,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20600013</t>
+          <t>20600011</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1735,12 +1743,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20600014</t>
+          <t>20600012</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1776,12 +1784,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20600015</t>
+          <t>20600013</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1817,12 +1825,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20600016</t>
+          <t>20600014</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1858,12 +1866,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20600017</t>
+          <t>20600015</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1899,12 +1907,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20600018</t>
+          <t>20600016</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1940,12 +1948,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20600019</t>
+          <t>20600017</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1981,40 +1989,40 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20800000</t>
+          <t>20600018</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>14000</v>
+        <v>5000</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>ATH160001</t>
+          <t>ATH160206</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>Struct</t>
+          <t>Border</t>
         </is>
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>Uring</t>
+          <t>Risk</t>
         </is>
       </c>
       <c r="BV25" t="inlineStr">
         <is>
-          <t>2080000000208</t>
+          <t>2060000000206</t>
         </is>
       </c>
       <c r="CK25" t="inlineStr"/>
@@ -2022,40 +2030,40 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20800001</t>
+          <t>20600019</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>14000</v>
+        <v>5000</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>ATH160001</t>
+          <t>ATH160206</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>Struct</t>
+          <t>Border</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>Uring</t>
+          <t>Risk</t>
         </is>
       </c>
       <c r="BV26" t="inlineStr">
         <is>
-          <t>2080000000208</t>
+          <t>2060000000206</t>
         </is>
       </c>
       <c r="CK26" t="inlineStr"/>
@@ -2063,7 +2071,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20800002</t>
+          <t>20800000</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2073,7 +2081,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -2104,7 +2112,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20800003</t>
+          <t>20800001</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2114,7 +2122,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="L28" t="n">
@@ -2145,7 +2153,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20800004</t>
+          <t>20800002</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2155,7 +2163,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="L29" t="n">
@@ -2186,7 +2194,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20800005</t>
+          <t>20800003</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2196,7 +2204,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="L30" t="n">
@@ -2227,7 +2235,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20800006</t>
+          <t>20800004</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2237,7 +2245,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="L31" t="n">
@@ -2268,7 +2276,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20800007</t>
+          <t>20800005</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2278,7 +2286,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="L32" t="n">
@@ -2309,7 +2317,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20800008</t>
+          <t>20800006</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2319,7 +2327,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="L33" t="n">
@@ -2350,7 +2358,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20800009</t>
+          <t>20800007</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2360,7 +2368,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="L34" t="n">
@@ -2391,7 +2399,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20800010</t>
+          <t>20800008</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2401,7 +2409,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="L35" t="n">
@@ -2432,21 +2440,21 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2090001</t>
+          <t>20800009</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>02:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>9000</v>
+        <v>14000</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -2455,17 +2463,17 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>Round</t>
+          <t>Struct</t>
         </is>
       </c>
       <c r="BI36" t="inlineStr">
         <is>
-          <t>Clock</t>
+          <t>Uring</t>
         </is>
       </c>
       <c r="BV36" t="inlineStr">
         <is>
-          <t>2090000000209</t>
+          <t>2080000000208</t>
         </is>
       </c>
       <c r="CK36" t="inlineStr"/>
@@ -2473,21 +2481,21 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2090002</t>
+          <t>20800010</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>9000</v>
+        <v>14000</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
@@ -2496,17 +2504,17 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>Round</t>
+          <t>Struct</t>
         </is>
       </c>
       <c r="BI37" t="inlineStr">
         <is>
-          <t>Clock</t>
+          <t>Uring</t>
         </is>
       </c>
       <c r="BV37" t="inlineStr">
         <is>
-          <t>2090000000209</t>
+          <t>2080000000208</t>
         </is>
       </c>
       <c r="CK37" t="inlineStr"/>
@@ -2514,43 +2522,125 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>2090001</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>02:00:00</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>9000</v>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>ATH160001</t>
+        </is>
+      </c>
+      <c r="BH38" t="inlineStr">
+        <is>
+          <t>Round</t>
+        </is>
+      </c>
+      <c r="BI38" t="inlineStr">
+        <is>
+          <t>Clock</t>
+        </is>
+      </c>
+      <c r="BV38" t="inlineStr">
+        <is>
+          <t>2090000000209</t>
+        </is>
+      </c>
+      <c r="CK38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2090002</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>9000</v>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>ATH160001</t>
+        </is>
+      </c>
+      <c r="BH39" t="inlineStr">
+        <is>
+          <t>Round</t>
+        </is>
+      </c>
+      <c r="BI39" t="inlineStr">
+        <is>
+          <t>Clock</t>
+        </is>
+      </c>
+      <c r="BV39" t="inlineStr">
+        <is>
+          <t>2090000000209</t>
+        </is>
+      </c>
+      <c r="CK39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>1520184591</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>13:00:00</t>
         </is>
       </c>
-      <c r="L38" t="n">
+      <c r="L40" t="n">
         <v>8000</v>
       </c>
-      <c r="V38" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>ATH160001</t>
         </is>
       </c>
-      <c r="BH38" t="inlineStr">
+      <c r="BH40" t="inlineStr">
         <is>
           <t>Tial Cuai Man</t>
         </is>
       </c>
-      <c r="BI38" t="inlineStr">
+      <c r="BI40" t="inlineStr">
         <is>
           <t>No Last Name</t>
         </is>
       </c>
-      <c r="BV38" t="inlineStr">
+      <c r="BV40" t="inlineStr">
         <is>
           <t>5050000000301</t>
         </is>
       </c>
-      <c r="CK38" t="inlineStr"/>
+      <c r="CK40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
